--- a/xls/square_un_16_tri3_12.xlsx
+++ b/xls/square_un_16_tri3_12.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>209</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>340</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>165</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>864</v>
+      </c>
+      <c r="I10">
+        <v>-0.00022051929664709843</v>
+      </c>
+      <c r="J10">
+        <v>-1.5469697661442632</v>
+      </c>
+      <c r="K10">
+        <v>-0.11037864670519405</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>209</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>340</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>174</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>906</v>
+      </c>
+      <c r="I11">
+        <v>-0.00021524637070380247</v>
+      </c>
+      <c r="J11">
+        <v>-1.3421410264296914</v>
+      </c>
+      <c r="K11">
+        <v>0.12147187518140676</v>
+      </c>
+    </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F12">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
       <c r="H12">
-        <v>864</v>
+        <v>1104</v>
       </c>
       <c r="I12">
-        <v>-1.491187793773586</v>
+        <v>-0.0002045568509750333</v>
       </c>
       <c r="J12">
-        <v>-1.6812702516716218</v>
+        <v>-1.1400142477729274</v>
       </c>
       <c r="K12">
-        <v>-0.6588434394575479</v>
+        <v>0.6676870837793687</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F13">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13">
-        <v>1014</v>
+        <v>1266</v>
       </c>
       <c r="I13">
-        <v>-1.9958609131642946</v>
+        <v>-0.0001876229344807105</v>
       </c>
       <c r="J13">
-        <v>-1.942496500337945</v>
+        <v>-0.8977650360748431</v>
       </c>
       <c r="K13">
-        <v>-0.8406498829978419</v>
+        <v>1.4729659102577224</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F14">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
       <c r="H14">
-        <v>1176</v>
+        <v>1362</v>
       </c>
       <c r="I14">
-        <v>-2.3899613128994632</v>
+        <v>-0.00017117809476641465</v>
       </c>
       <c r="J14">
-        <v>-1.980505815696123</v>
+        <v>-0.7460914669301223</v>
       </c>
       <c r="K14">
-        <v>-0.6689015764919019</v>
+        <v>1.7284932048454673</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F15">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>1350</v>
+        <v>1596</v>
       </c>
       <c r="I15">
-        <v>-2.2953368466352684</v>
+        <v>-0.00014949170662173811</v>
       </c>
       <c r="J15">
-        <v>-1.8033474708185242</v>
+        <v>-0.5629712143967371</v>
       </c>
       <c r="K15">
-        <v>-0.3281488199379987</v>
+        <v>2.5600956862696793</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1536</v>
+        <v>1842</v>
       </c>
       <c r="I16">
-        <v>-1.8824222344856303</v>
+        <v>-7.194839894278435e-5</v>
       </c>
       <c r="J16">
-        <v>-1.556909938468298</v>
+        <v>-0.23697993227628203</v>
       </c>
       <c r="K16">
-        <v>0.006719897092661723</v>
+        <v>3.100676562765435</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>1734</v>
+        <v>2070</v>
       </c>
       <c r="I17">
-        <v>-1.5960791809865225</v>
+        <v>-1.8994736885376128e-5</v>
       </c>
       <c r="J17">
-        <v>-1.3701088483198847</v>
+        <v>-0.05652575600825685</v>
       </c>
       <c r="K17">
-        <v>0.503853783596401</v>
+        <v>3.365351966370223</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B18">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-0.9232457483939006</v>
+        <v>-1.804167107622886e-8</v>
       </c>
       <c r="J18">
-        <v>-0.7792170346827093</v>
+        <v>-4.2664329058479267e-5</v>
       </c>
       <c r="K18">
-        <v>1.287332889112537</v>
+        <v>2.245040813885171</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-0.2567852335439675</v>
+        <v>-2.2912022398500757e-9</v>
       </c>
       <c r="J19">
-        <v>-0.25263653154578897</v>
+        <v>-4.869666807988034e-6</v>
       </c>
       <c r="K19">
-        <v>2.0844134072224567</v>
+        <v>1.7946475738686742</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>0.0003324383293703821</v>
+        <v>-1.3062995408765471e-9</v>
       </c>
       <c r="J20">
-        <v>-0.00040180161793859274</v>
+        <v>-2.6819168121088832e-6</v>
       </c>
       <c r="K20">
-        <v>2.812401792605622</v>
+        <v>1.6639811500753479</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.2965491169631653e-6</v>
+        <v>-9.303747028618345e-10</v>
       </c>
       <c r="J21">
-        <v>-1.985163546053087e-5</v>
+        <v>-1.9864631318583495e-6</v>
       </c>
       <c r="K21">
-        <v>2.2906791635732064</v>
+        <v>1.6029236581445967</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-8.509662651049383e-6</v>
+        <v>-8.382520176306849e-10</v>
       </c>
       <c r="J22">
-        <v>-1.3025267504539068e-5</v>
+        <v>-1.8097514565578154e-6</v>
       </c>
       <c r="K22">
-        <v>2.1013511057708385</v>
+        <v>1.5844759653040537</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-3.291419630761429e-6</v>
+        <v>-6.642040244702994e-10</v>
       </c>
       <c r="J23">
-        <v>-5.248324990393165e-6</v>
+        <v>-1.417319470922454e-6</v>
       </c>
       <c r="K23">
-        <v>1.901834056903629</v>
+        <v>1.5325904752367712</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-3.095515104267713e-6</v>
+        <v>-6.375969277861368e-10</v>
       </c>
       <c r="J24">
-        <v>-4.8194884874356685e-6</v>
+        <v>-1.3734116716910768e-6</v>
       </c>
       <c r="K24">
-        <v>1.876717798358229</v>
+        <v>1.5256479995282817</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -916,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-1.4906933163444054e-6</v>
+        <v>-5.623787102618381e-10</v>
       </c>
       <c r="J25">
-        <v>-2.745143092896804e-6</v>
+        <v>-1.2034260777174852e-6</v>
       </c>
       <c r="K25">
-        <v>1.7771868382813663</v>
+        <v>1.4972488127926786</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -951,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-2.0539481133794677e-6</v>
+        <v>-5.218914215280576e-10</v>
       </c>
       <c r="J26">
-        <v>-3.032828466156605e-6</v>
+        <v>-1.1197944082505262e-6</v>
       </c>
       <c r="K26">
-        <v>1.7705104344418403</v>
+        <v>1.481851265489309</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -986,7 +1056,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -998,22 +1068,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-1.312284230453365e-6</v>
+        <v>-5.045863722548148e-10</v>
       </c>
       <c r="J27">
-        <v>-2.043497801281553e-6</v>
+        <v>-1.088016040654749e-6</v>
       </c>
       <c r="K27">
-        <v>1.690486574851212</v>
+        <v>1.4762326401400627</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1021,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1033,22 +1103,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-1.6059366192371056e-6</v>
+        <v>-4.978868036059503e-10</v>
       </c>
       <c r="J28">
-        <v>-2.115879955089407e-6</v>
+        <v>-1.0793426004472894e-6</v>
       </c>
       <c r="K28">
-        <v>1.6732451534658495</v>
+        <v>1.4747874535633085</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1056,7 +1126,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -1068,22 +1138,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-1.323893381295893e-6</v>
+        <v>-4.949861065832423e-10</v>
       </c>
       <c r="J29">
-        <v>-1.6830127551793434e-6</v>
+        <v>-1.0680328084728212e-6</v>
       </c>
       <c r="K29">
-        <v>1.6178700544416744</v>
+        <v>1.4722701836287815</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1091,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1103,22 +1173,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-1.3595646075013814e-6</v>
+        <v>-4.6136116498046677e-10</v>
       </c>
       <c r="J30">
-        <v>-1.5849031763546408e-6</v>
+        <v>-1.0002882991863013e-6</v>
       </c>
       <c r="K30">
-        <v>1.588055512180537</v>
+        <v>1.458335180069586</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1126,7 +1196,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1138,22 +1208,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-1.272198033057996e-6</v>
+        <v>-4.5188206705614817e-10</v>
       </c>
       <c r="J31">
-        <v>-1.461823851953626e-6</v>
+        <v>-9.811149522028625e-7</v>
       </c>
       <c r="K31">
-        <v>1.5675366535852977</v>
+        <v>1.4543471361742764</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1161,7 +1231,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1173,22 +1243,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-1.2344341443767918e-6</v>
+        <v>-4.437216869438934e-10</v>
       </c>
       <c r="J32">
-        <v>-1.3863105894127367e-6</v>
+        <v>-9.632554740998673e-7</v>
       </c>
       <c r="K32">
-        <v>1.549886239014801</v>
+        <v>1.450426661004296</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_12.xlsx
+++ b/xls/square_un_16_tri3_12.xlsx
@@ -482,13 +482,13 @@
         <v>864</v>
       </c>
       <c r="I10">
-        <v>-0.00022051929664709843</v>
+        <v>-0.9086173080798292</v>
       </c>
       <c r="J10">
-        <v>-1.5469697661442632</v>
+        <v>-1.5935840638935228</v>
       </c>
       <c r="K10">
-        <v>-0.11037864670519405</v>
+        <v>-0.6787010940746232</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -517,13 +517,13 @@
         <v>906</v>
       </c>
       <c r="I11">
-        <v>-0.00021524637070380247</v>
+        <v>-1.8178817359700254</v>
       </c>
       <c r="J11">
-        <v>-1.3421410264296914</v>
+        <v>-1.8081835777587354</v>
       </c>
       <c r="K11">
-        <v>0.12147187518140676</v>
+        <v>-0.8240503535722978</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1104</v>
       </c>
       <c r="I12">
-        <v>-0.0002045568509750333</v>
+        <v>-2.3259700093170963</v>
       </c>
       <c r="J12">
-        <v>-1.1400142477729274</v>
+        <v>-1.9777530866541748</v>
       </c>
       <c r="K12">
-        <v>0.6676870837793687</v>
+        <v>-1.0230374410278935</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1266</v>
       </c>
       <c r="I13">
-        <v>-0.0001876229344807105</v>
+        <v>-2.349797950180721</v>
       </c>
       <c r="J13">
-        <v>-0.8977650360748431</v>
+        <v>-1.9067628407038437</v>
       </c>
       <c r="K13">
-        <v>1.4729659102577224</v>
+        <v>-0.7295153449029245</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1362</v>
       </c>
       <c r="I14">
-        <v>-0.00017117809476641465</v>
+        <v>-2.27384994708079</v>
       </c>
       <c r="J14">
-        <v>-0.7460914669301223</v>
+        <v>-1.8318642348322038</v>
       </c>
       <c r="K14">
-        <v>1.7284932048454673</v>
+        <v>-0.527901782107751</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1596</v>
       </c>
       <c r="I15">
-        <v>-0.00014949170662173811</v>
+        <v>-1.910721819176484</v>
       </c>
       <c r="J15">
-        <v>-0.5629712143967371</v>
+        <v>-1.5613447508407514</v>
       </c>
       <c r="K15">
-        <v>2.5600956862696793</v>
+        <v>-0.04502813087392008</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-7.194839894278435e-5</v>
+        <v>-1.7875953718742366</v>
       </c>
       <c r="J16">
-        <v>-0.23697993227628203</v>
+        <v>-1.5548875252985772</v>
       </c>
       <c r="K16">
-        <v>3.100676562765435</v>
+        <v>-0.16607629297972368</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-1.8994736885376128e-5</v>
+        <v>-0.6519024726642092</v>
       </c>
       <c r="J17">
-        <v>-0.05652575600825685</v>
+        <v>-0.6033171937701278</v>
       </c>
       <c r="K17">
-        <v>3.365351966370223</v>
+        <v>1.5177317038208746</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-1.804167107622886e-8</v>
+        <v>-0.02089612298152744</v>
       </c>
       <c r="J18">
-        <v>-4.2664329058479267e-5</v>
+        <v>-0.020579039217739497</v>
       </c>
       <c r="K18">
-        <v>2.245040813885171</v>
+        <v>2.7703504378570623</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-2.2912022398500757e-9</v>
+        <v>-2.451373732000569e-6</v>
       </c>
       <c r="J19">
-        <v>-4.869666807988034e-6</v>
+        <v>-4.617361734463745e-6</v>
       </c>
       <c r="K19">
-        <v>1.7946475738686742</v>
+        <v>1.878741624538169</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -832,13 +832,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-1.3062995408765471e-9</v>
+        <v>-1.932872252672943e-6</v>
       </c>
       <c r="J20">
-        <v>-2.6819168121088832e-6</v>
+        <v>-2.6149993553386877e-6</v>
       </c>
       <c r="K20">
-        <v>1.6639811500753479</v>
+        <v>1.714403240548491</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -867,13 +867,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-9.303747028618345e-10</v>
+        <v>-1.3588432816450226e-6</v>
       </c>
       <c r="J21">
-        <v>-1.9864631318583495e-6</v>
+        <v>-1.9355688239921155e-6</v>
       </c>
       <c r="K21">
-        <v>1.6029236581445967</v>
+        <v>1.655501155951839</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -902,13 +902,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-8.382520176306849e-10</v>
+        <v>-1.6501756587653333e-6</v>
       </c>
       <c r="J22">
-        <v>-1.8097514565578154e-6</v>
+        <v>-1.8613411053766076e-6</v>
       </c>
       <c r="K22">
-        <v>1.5844759653040537</v>
+        <v>1.6075571892710752</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -937,13 +937,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-6.642040244702994e-10</v>
+        <v>-1.195914783570912e-6</v>
       </c>
       <c r="J23">
-        <v>-1.417319470922454e-6</v>
+        <v>-1.3839921429819423e-6</v>
       </c>
       <c r="K23">
-        <v>1.5325904752367712</v>
+        <v>1.5488856403728095</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -972,13 +972,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-6.375969277861368e-10</v>
+        <v>-1.1582333430139683e-6</v>
       </c>
       <c r="J24">
-        <v>-1.3734116716910768e-6</v>
+        <v>-1.35578493057393e-6</v>
       </c>
       <c r="K24">
-        <v>1.5256479995282817</v>
+        <v>1.5460693085711983</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-5.623787102618381e-10</v>
+        <v>-1.1230952848124752e-6</v>
       </c>
       <c r="J25">
-        <v>-1.2034260777174852e-6</v>
+        <v>-1.2301949723347413e-6</v>
       </c>
       <c r="K25">
-        <v>1.4972488127926786</v>
+        <v>1.5115105752845546</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-5.218914215280576e-10</v>
+        <v>-1.0743351823661242e-6</v>
       </c>
       <c r="J26">
-        <v>-1.1197944082505262e-6</v>
+        <v>-1.1586364567891384e-6</v>
       </c>
       <c r="K26">
-        <v>1.481851265489309</v>
+        <v>1.4952608247357408</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-5.045863722548148e-10</v>
+        <v>-1.0462205249870324e-6</v>
       </c>
       <c r="J27">
-        <v>-1.088016040654749e-6</v>
+        <v>-1.1253621205018883e-6</v>
       </c>
       <c r="K27">
-        <v>1.4762326401400627</v>
+        <v>1.4877574301228782</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-4.978868036059503e-10</v>
+        <v>-1.0697603592379686e-6</v>
       </c>
       <c r="J28">
-        <v>-1.0793426004472894e-6</v>
+        <v>-1.1364174403997887e-6</v>
       </c>
       <c r="K28">
-        <v>1.4747874535633085</v>
+        <v>1.4870982904745504</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-4.949861065832423e-10</v>
+        <v>-1.041470147268778e-6</v>
       </c>
       <c r="J29">
-        <v>-1.0680328084728212e-6</v>
+        <v>-1.1194105077731593e-6</v>
       </c>
       <c r="K29">
-        <v>1.4722701836287815</v>
+        <v>1.486937764947149</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-4.6136116498046677e-10</v>
+        <v>-1.0072124807121898e-6</v>
       </c>
       <c r="J30">
-        <v>-1.0002882991863013e-6</v>
+        <v>-1.0634578764900002e-6</v>
       </c>
       <c r="K30">
-        <v>1.458335180069586</v>
+        <v>1.4712981381602501</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-4.5188206705614817e-10</v>
+        <v>-1.0046306862544396e-6</v>
       </c>
       <c r="J31">
-        <v>-9.811149522028625e-7</v>
+        <v>-1.0535206151539521e-6</v>
       </c>
       <c r="K31">
-        <v>1.4543471361742764</v>
+        <v>1.4678471660917767</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1252,13 +1252,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-4.437216869438934e-10</v>
+        <v>-9.630685790184429e-7</v>
       </c>
       <c r="J32">
-        <v>-9.632554740998673e-7</v>
+        <v>-1.0185403552746147e-6</v>
       </c>
       <c r="K32">
-        <v>1.450426661004296</v>
+        <v>1.462319044331759</v>
       </c>
     </row>
   </sheetData>
